--- a/cp-upgrade-mhd/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/cp-upgrade-mhd/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="345">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:39:30+00:00</t>
+    <t>2026-05-05T15:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -888,10 +888,6 @@
   </si>
   <si>
     <t>A list is a curated collection of resources.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}</t>
   </si>
   <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>
@@ -7663,13 +7659,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7680,7 +7676,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>195</v>
@@ -7792,7 +7788,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>199</v>
@@ -7904,7 +7900,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>200</v>
@@ -8018,7 +8014,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>201</v>
@@ -8134,7 +8130,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>202</v>
@@ -8248,7 +8244,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>208</v>
@@ -8362,7 +8358,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>213</v>
@@ -8474,7 +8470,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>217</v>
@@ -8586,7 +8582,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>218</v>
@@ -8700,7 +8696,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>219</v>
@@ -8816,7 +8812,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>220</v>
@@ -8928,7 +8924,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -9042,7 +9038,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9154,7 +9150,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9266,7 +9262,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -9378,7 +9374,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -9490,7 +9486,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -9602,7 +9598,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -9714,7 +9710,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -9828,7 +9824,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -9944,7 +9940,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -10056,7 +10052,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10168,7 +10164,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10282,7 +10278,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -10396,7 +10392,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -10510,13 +10506,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10541,7 +10537,7 @@
         <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>177</v>
@@ -10624,7 +10620,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>181</v>
@@ -10736,7 +10732,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>182</v>
@@ -10850,7 +10846,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>183</v>
@@ -10966,7 +10962,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>184</v>
@@ -11078,7 +11074,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>187</v>
@@ -11192,7 +11188,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>191</v>
@@ -11218,7 +11214,7 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>276</v>
@@ -11287,13 +11283,13 @@
         <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11304,7 +11300,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -11416,7 +11412,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -11528,7 +11524,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -11642,7 +11638,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -11758,7 +11754,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -11872,7 +11868,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -11986,7 +11982,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12098,7 +12094,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12210,7 +12206,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12324,7 +12320,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -12440,7 +12436,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -12552,7 +12548,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -12666,7 +12662,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -12778,7 +12774,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -12890,7 +12886,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13002,7 +12998,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13114,7 +13110,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13226,7 +13222,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13338,7 +13334,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -13452,7 +13448,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -13568,7 +13564,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -13680,7 +13676,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -13792,7 +13788,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -13906,7 +13902,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14020,7 +14016,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14134,10 +14130,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14160,19 +14156,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14221,7 +14217,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
